--- a/src/test/resource/ExcelData/PractoCred1.xlsx
+++ b/src/test/resource/ExcelData/PractoCred1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manvsriv\Practo\PractoAutomation\src\test\resource\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{858B071E-3155-44CD-8562-05E55FC7EBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E245D0-EAEE-48B9-8335-F2821CD2AECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/src/test/resource/ExcelData/PractoCred1.xlsx
+++ b/src/test/resource/ExcelData/PractoCred1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manvsriv\Practo\PractoAutomation\src\test\resource\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E245D0-EAEE-48B9-8335-F2821CD2AECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDB61D8-575A-4976-AA81-6BB32F418E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2970" yWindow="1870" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>name</t>
   </si>
@@ -37,6 +37,9 @@
   </si>
   <si>
     <t>AA</t>
+  </si>
+  <si>
+    <t>AS</t>
   </si>
 </sst>
 </file>
@@ -354,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
@@ -384,6 +387,11 @@
         <v>1234567890</v>
       </c>
     </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
